--- a/extenbooks/XS2303_extenbook.xlsx
+++ b/extenbooks/XS2303_extenbook.xlsx
@@ -628,7 +628,7 @@
         <v>1991</v>
       </c>
       <c r="B5" t="n">
-        <v>43.6742991031197</v>
+        <v>43.6742991031198</v>
       </c>
     </row>
     <row r="6">
@@ -636,7 +636,7 @@
         <v>1992</v>
       </c>
       <c r="B6" t="n">
-        <v>20.6203619151071</v>
+        <v>20.6203619151072</v>
       </c>
     </row>
     <row r="7">
@@ -692,7 +692,7 @@
         <v>1999</v>
       </c>
       <c r="B13" t="n">
-        <v>157.727874491998</v>
+        <v>157.727874491999</v>
       </c>
     </row>
     <row r="14">
@@ -708,7 +708,7 @@
         <v>2001</v>
       </c>
       <c r="B15" t="n">
-        <v>215.605127617139</v>
+        <v>215.60512761714</v>
       </c>
     </row>
     <row r="16">
@@ -716,7 +716,7 @@
         <v>2002</v>
       </c>
       <c r="B16" t="n">
-        <v>291.127828205211</v>
+        <v>291.127828205212</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         <v>2003</v>
       </c>
       <c r="B17" t="n">
-        <v>408.150659048592</v>
+        <v>408.150659048593</v>
       </c>
     </row>
     <row r="18">
@@ -732,7 +732,7 @@
         <v>2004</v>
       </c>
       <c r="B18" t="n">
-        <v>614.4995243495999</v>
+        <v>614.499524349601</v>
       </c>
     </row>
     <row r="19">
@@ -748,7 +748,7 @@
         <v>2006</v>
       </c>
       <c r="B20" t="n">
-        <v>1068.49302986989</v>
+        <v>1068.4930298699</v>
       </c>
     </row>
     <row r="21">
@@ -756,7 +756,7 @@
         <v>2007</v>
       </c>
       <c r="B21" t="n">
-        <v>1530.28162304336</v>
+        <v>1530.28162304337</v>
       </c>
     </row>
     <row r="22">
@@ -804,7 +804,7 @@
         <v>2013</v>
       </c>
       <c r="B27" t="n">
-        <v>3839.54776025292</v>
+        <v>3839.54776025293</v>
       </c>
     </row>
     <row r="28">
@@ -812,7 +812,7 @@
         <v>2014</v>
       </c>
       <c r="B28" t="n">
-        <v>3859.16796299108</v>
+        <v>3859.16796299109</v>
       </c>
     </row>
     <row r="29">
@@ -820,7 +820,7 @@
         <v>2015</v>
       </c>
       <c r="B29" t="n">
-        <v>3345.19376388813</v>
+        <v>3345.19376388814</v>
       </c>
     </row>
     <row r="30">
@@ -876,7 +876,7 @@
         <v>2022</v>
       </c>
       <c r="B36" t="n">
-        <v>3189.68910881377</v>
+        <v>3189.68910881378</v>
       </c>
     </row>
     <row r="37">
@@ -960,7 +960,7 @@
         <v>1991</v>
       </c>
       <c r="B45" t="n">
-        <v>43.6742991031197</v>
+        <v>43.6742991031198</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>1992</v>
       </c>
       <c r="B46" t="n">
-        <v>20.6203619151071</v>
+        <v>20.6203619151072</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>1999</v>
       </c>
       <c r="B53" t="n">
-        <v>157.727874491998</v>
+        <v>157.727874491999</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>2001</v>
       </c>
       <c r="B55" t="n">
-        <v>215.605127617139</v>
+        <v>215.60512761714</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>2002</v>
       </c>
       <c r="B56" t="n">
-        <v>291.127828205211</v>
+        <v>291.127828205212</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>2003</v>
       </c>
       <c r="B57" t="n">
-        <v>408.150659048592</v>
+        <v>408.150659048593</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>2004</v>
       </c>
       <c r="B58" t="n">
-        <v>614.4995243495999</v>
+        <v>614.499524349601</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>2006</v>
       </c>
       <c r="B60" t="n">
-        <v>1068.49302986989</v>
+        <v>1068.4930298699</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>2007</v>
       </c>
       <c r="B61" t="n">
-        <v>1530.28162304336</v>
+        <v>1530.28162304337</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>2013</v>
       </c>
       <c r="B67" t="n">
-        <v>3839.54776025292</v>
+        <v>3839.54776025293</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>2014</v>
       </c>
       <c r="B68" t="n">
-        <v>3859.16796299108</v>
+        <v>3859.16796299109</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>2015</v>
       </c>
       <c r="B69" t="n">
-        <v>3345.19376388813</v>
+        <v>3345.19376388814</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>2022</v>
       </c>
       <c r="B76" t="n">
-        <v>3189.68910881377</v>
+        <v>3189.68910881378</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A158"/>
+  <dimension ref="A1:A153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1788,35 +1788,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Series ID**: XS2303</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>**Series ID**: XS2303</t>
+          <t>**Status**: study_complete</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: study_complete</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>**Author**: opus-fanout-ES</t>
+          <t>## 1. Definition</t>
         </is>
       </c>
     </row>
@@ -1826,38 +1822,38 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>## 1. Definition</t>
+          <t>XS2303 is the annual time series of China's official foreign exchange</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>reserves, **excluding gold**, in current US Dollars. The paper source is</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XS2303 is the annual time series of China's official foreign exchange</t>
+          <t>Weber &amp; Shaikh (2020), Appendix Figure 3 (p. 454), which plots the</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>reserves, **excluding gold**, in current US Dollars. The paper source is</t>
+          <t>1990–2016 trajectory as a single dotted line. We extend to 2024.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Weber &amp; Shaikh (2020), Appendix Figure 3 (p. 454), which plots the</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1990–2016 trajectory as a single dotted line. We extend to 2024.</t>
+          <t>## 2. Why it matters</t>
         </is>
       </c>
     </row>
@@ -1867,52 +1863,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>## 2. Why it matters</t>
+          <t>Weber &amp; Shaikh use China's reserve accumulation as the empirical anchor</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>for their critique of the currency-manipulation argument. Section 1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Weber &amp; Shaikh use China's reserve accumulation as the empirical anchor</t>
+          <t>narrates the 17-fold rise from 2000–2010 to a 2013 level of USD 3.6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>for their critique of the currency-manipulation argument. Section 1</t>
+          <t>trillion; Section 3 (p. 438) notes the 2014 peak near USD 4 trillion</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>narrates the 17-fold rise from 2000–2010 to a 2013 level of USD 3.6</t>
+          <t>and subsequent stabilisation around USD 3 trillion. The series is the</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>trillion; Section 3 (p. 438) notes the 2014 peak near USD 4 trillion</t>
+          <t>single most-cited empirical fact in the paper's headline narrative.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>and subsequent stabilisation around USD 3 trillion. The series is the</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>single most-cited empirical fact in the paper's headline narrative.</t>
+          <t>## 3. Sources</t>
         </is>
       </c>
     </row>
@@ -1922,31 +1918,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>|---|---|---|---|---|</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+          <t>| XS2303-A | 1990–2024 | World Bank World Development Indicators (WDI) indicator `FI.RES.XGLD.CD` (Total reserves minus gold, current US$) for country `CHN` | current USD | World Bank Data API (`api.worldbank.org/v2/country/CHN/indicator/FI.RES.XGLD.CD?format=json`); no auth; CC-BY-4.0 |</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>| XS2303-A | 1990–2024 | World Bank WDI indicator `FI.RES.XGLD.CD` (Total reserves minus gold, current US$) for country `CHN` | current USD | World Bank Data API (`api.worldbank.org/v2/country/CHN/indicator/FI.RES.XGLD.CD?format=json`); no auth; CC-BY-4.0 |</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
@@ -1956,189 +1952,189 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>Direct pass-through. The WDI series is the canonical source the paper</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cites ("Data sourcre: World Bank, 2018" sic on Fig 3). The loader fetches</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Direct pass-through. The WDI series is the canonical source the paper</t>
+          <t>the WDI series via the open Data API, divides by 1e9 to convert current USD →</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cites ("Data sourcre: World Bank, 2018" sic on Fig 3). Phase 5 loader</t>
+          <t>Billion USD (the paper's plotted unit), and emits a single subseries</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>fetches WDI raw via the open Data API, divides by 1e9 to convert</t>
+          <t>`XS2303-A` (this series has one component, suffixed `-A`).</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>current USD → Billion USD (the paper's plotted unit), and writes one</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>parquet with columns `year, value, subseries_id='XS2303-A',</t>
+          <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>source_id='WB_FI_RES_XGLD_CD_CHN', units='billion_usd'`.</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>- Paper window: 1990–2016 (27 obs)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>- Extension: 2017–2024 (8 obs; subject to WDI release lag)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>- Total: 1990–2024 (35 obs)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>- Paper window: 1990–2016 (27 obs)</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>- Extension: 2017–2024 (8 obs; subject to WDI release lag)</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>- Total: 1990–2024 (35 obs)</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Billion current USD. (WDI raw is current USD; loader divides by 1e9.)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>## 6. Units</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>## 7. Caveats</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Billion current USD. (WDI raw is current USD; loader divides by 1e9.)</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1. WDI's `FI.RES.XGLD.CD` sources from IMF International Financial</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t xml:space="preserve">   Statistics; it excludes gold and excludes sovereign-wealth-fund</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   holdings (China Investment Corporation, CIC). Do not substitute</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1. WDI's `FI.RES.XGLD.CD` sources from IMF International Financial</t>
+          <t xml:space="preserve">   `FI.RES.TOTL.CD` (with gold) — the</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Statistics; it excludes gold and excludes sovereign-wealth-fund</t>
+          <t xml:space="preserve">   paper's figure title is unambiguous "without Gold".</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">   holdings (CIC). Do not substitute `FI.RES.TOTL.CD` (with gold) — the</t>
+          <t>2. WDI release lag: typical 6–12 months from current year-end. If the</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">   paper's figure title is unambiguous "without Gold".</t>
+          <t xml:space="preserve">   API returns NaN for the most-recent year, the loader propagates</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2. WDI release lag: typical 6–12 months from current year-end. If the</t>
+          <t xml:space="preserve">   NaN — no carry-forward.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">   API returns NaN for the most-recent year, the loader propagates</t>
+          <t>3. Headline anchors from paper text (p. 433): 17-fold rise 2000→2010</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">   NaN — no carry-forward.</t>
+          <t xml:space="preserve">   (WDI: 168 → 2914 bn USD = 17.3x); 2013 ≈ USD 3.6 trillion (WDI: ~3880);</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3. Headline anchors from paper text (p. 433): 17-fold rise 2000→2010</t>
+          <t xml:space="preserve">   2014 peak ≈ USD 4 trillion (WDI: ~3843).</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   (WDI: 168 → 2914 bn USD = 17.3x); 2013 ≈ USD 3.6 trillion (WDI: ~3880);</t>
-        </is>
-      </c>
+      <c r="A64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">   2014 peak ≈ USD 4 trillion (WDI: ~3843).</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
@@ -2148,226 +2144,222 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>- Related: XS2301 (Fig 1 trade balance), XS2302 (Fig 2 CA balance),</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  XS2304/XS2305 (literature-compilation Figs 4/5)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>- Dossier: `Technical/research/XS2303_research.json`</t>
+          <t>- Book chapter ancestor: S1101 (Ch11 trade balances), but distinct</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>- Adequacy: `Technical/docs/chapters/CHES_v2_ADEQUACY_REPORT.json` (5-way split)</t>
+          <t xml:space="preserve">  concept (FX reserves vs trade-balance ratio)</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>- Related: XS2301 (Fig 1 trade balance), XS2302 (Fig 2 CA balance),</t>
-        </is>
-      </c>
+      <c r="A71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  XS2304/XS2305 (literature-compilation Figs 4/5)</t>
+          <t>## 9. Validation expectation</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>- Book chapter ancestor: S1101 (Ch11 trade balances), but distinct</t>
-        </is>
-      </c>
+      <c r="A73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">  concept (FX reserves vs trade-balance ratio)</t>
+          <t>- Tolerance: ±1.0% per year against the WDI series values.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>- The validator compares the processed parquet against a fresh API pull;</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>- Tolerance: ±1.0% per year against the WDI series values.</t>
+          <t xml:space="preserve">  identity match expected since construction is direct pass-through.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>- The validator compares the processed parquet against a fresh API pull;</t>
-        </is>
+      <c r="A79" s="4">
+        <f>== EPR: XS2303_EPR.md ===</f>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">  identity match expected since construction is direct pass-through.</t>
+          <t># XS2303 — Extension Provenance Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>**Series**: XS2303 — China FX Reserves Excluding Gold</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4">
-        <f>== EPR: XS2303_EPR.md ===</f>
-        <v/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>**Construction classification**: `direct`</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t># XS2303 — Extension Provenance Record</t>
+          <t>**Extension method**: continuation of the same World Bank World Development</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Indicators (WDI) series the paper cites</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>**Series**: XS2303 — China FX Reserves Excluding Gold</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
+      <c r="A87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>**Construction classification**: `direct`</t>
+          <t>## 1. Why this series is extendable</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>**Extension method**: continuation of the same WDI series the paper cites</t>
-        </is>
-      </c>
+      <c r="A89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t>WDI indicator `FI.RES.XGLD.CD` is continuously published; China's</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>reserves have been reported since 1990. Extension to 2024 requires no</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>## 1. Why this series is extendable</t>
+          <t>methodological change — it is the *same series* Weber &amp; Shaikh cited</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>(2018 vintage), pulled at a later vintage.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>WDI indicator `FI.RES.XGLD.CD` is continuously published; China's</t>
-        </is>
-      </c>
+      <c r="A94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>reserves have been reported since 1990. Extension to 2024 requires no</t>
+          <t>## 2. Method</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>methodological change — it is the *same series* Weber &amp; Shaikh cited</t>
-        </is>
-      </c>
+      <c r="A96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>(2018 vintage), pulled at a later vintage.</t>
+          <t>1. The loader pulls World Bank indicator `FI.RES.XGLD.CD` for China (`CHN`),</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   1990–2024.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>## 2. Method</t>
+          <t>2. API returns the full annual series; values divided by 1e9 for</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   billion-USD presentation.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1. Loader calls `S00_apis.worldbank_indicator(country='CHN',</t>
+          <t>3. No splice, no rebase, no anchor — direct continuation.</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   indicator='FI.RES.XGLD.CD', start=1990, end=2024)`.</t>
-        </is>
-      </c>
+      <c r="A102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2. API returns the full annual series; values divided by 1e9 for</t>
+          <t>## 3. Proxies</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   billion-USD presentation.</t>
-        </is>
-      </c>
+      <c r="A104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3. No splice, no rebase, no anchor — direct continuation.</t>
+          <t>None. WDI IS the source the paper cites.</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2369,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>## 3. Proxies</t>
+          <t>## 4. Synthetic data</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2379,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>None. WDI IS the source the paper cites.</t>
+          <t>None permitted. NaN at any year propagates.</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2389,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>## 4. Synthetic data</t>
+          <t>## 5. Failure modes</t>
         </is>
       </c>
     </row>
@@ -2407,292 +2399,265 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>None permitted. NaN at any year propagates.</t>
+          <t>| Failure | Action |</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>|---|---|</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>## 5. Failure modes</t>
+          <t>| World Bank API non-200 | Loader retries 3x; if still failing, raises ApiUnavailable; processor publishes empty series with `status=degraded` |</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>| WDI vintage revision changes historical values | Acceptable — we use the latest vintage; pin `data_vintage_pulled_at` in cache metadata |</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>| Failure | Action |</t>
+          <t>| Indicator code change (unlikely for FI.RES.XGLD.CD) | Loader fails; surface as blocker, do not silently substitute |</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>|---|---|</t>
-        </is>
-      </c>
+      <c r="A118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>| World Bank API non-200 | Loader retries 3x; if still failing, raises ApiUnavailable; processor publishes empty series with `status=degraded` |</t>
+          <t>## 6. Conceptual continuity vs adjacent concepts</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>| WDI vintage revision changes historical values | Acceptable — we use the latest vintage; pin `data_vintage_pulled_at` in cache metadata |</t>
-        </is>
-      </c>
+      <c r="A120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>| Indicator code change (unlikely for FI.RES.XGLD.CD) | Loader fails; surface as blocker, do not silently substitute |</t>
+          <t>The extension proxy `World Bank WDI indicator FI.RES.XGLD.CD for country</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>CHN` measures `China's official foreign exchange reserves excluding gold`</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>## 6. Conceptual continuity vs adjacent concepts</t>
+          <t>rather than `total reserves including gold` or `sovereign-wealth-fund</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>assets (China Investment Corporation, CIC)` because:</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>The extension proxy `World Bank WDI indicator FI.RES.XGLD.CD for country</t>
+          <t>- Source agency choice: Weber &amp; Shaikh (2020) Fig 3 explicitly cites</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CHN` measures `China's official foreign exchange reserves excluding gold`</t>
+          <t xml:space="preserve">  "World Bank, 2018" with title "without Gold". WDI is the published</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>rather than `total reserves including gold` or `sovereign-wealth-fund</t>
+          <t xml:space="preserve">  recipe.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>assets (CIC)` because:</t>
+          <t>- Methodology continuity: paper-window 1990-2016 values came from WDI</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>- Source agency choice: Weber &amp; Shaikh (2020) Fig 3 explicitly cites</t>
+          <t xml:space="preserve">  FI.RES.XGLD.CD; extension years 2017-2024 use the *same* indicator at</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "World Bank, 2018" with title "without Gold". WDI is the published</t>
+          <t xml:space="preserve">  current vintage. Underlying source is IMF International Financial</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">  recipe.</t>
+          <t xml:space="preserve">  Statistics, intermediated by WDI — same data, same provider chain.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>- Methodology continuity: paper-window 1990-2016 values came from WDI</t>
+          <t>- Disambiguation: ex-gold reserves (FI.RES.XGLD.CD) ≠ total reserves</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FI.RES.XGLD.CD; extension years 2017-2024 use the *same* indicator at</t>
+          <t xml:space="preserve">  (FI.RES.TOTL.CD); reserves ≠ sovereign-wealth-fund assets (CIC, ~$1T,</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">  current vintage. Underlying source is IMF International Financial</t>
+          <t xml:space="preserve">  not in IFS); reserves ≠ banking-system FX assets (broader). The</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Statistics, intermediated by WDI — same data, same provider chain.</t>
+          <t xml:space="preserve">  ex-gold filter is critical because gold valuation effects would</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>- Disambiguation: ex-gold reserves (FI.RES.XGLD.CD) ≠ total reserves</t>
+          <t xml:space="preserve">  otherwise contaminate the trajectory.</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (FI.RES.TOTL.CD); reserves ≠ sovereign-wealth-fund assets (CIC, ~$1T,</t>
-        </is>
-      </c>
+      <c r="A137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">  not in IFS); reserves ≠ banking-system FX assets (broader). The</t>
+          <t>The book's original concept (Weber &amp; Shaikh 2020 p. 433) was: "China's</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ex-gold filter is critical because gold valuation effects would</t>
+          <t>reserves rose 17-fold from 2000 to 2010, reaching USD 3.6 trillion by</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">  otherwise contaminate the trajectory.</t>
+          <t>2013, peaking near USD 4 trillion in 2014, and stabilising around</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>USD 3 trillion thereafter". The modern series preserves the ex-gold,</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>The book's original concept (Weber &amp; Shaikh 2020 p. 433) was: "China's</t>
+          <t>official-sector, USD-denominated reserve concept while permitting WDI</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>reserves rose 17-fold from 2000 to 2010, reaching USD 3.6 trillion by</t>
+          <t>vintage revisions to shift historical values within tolerance. This is</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2013, peaking near USD 4 trillion in 2014, and stabilising around</t>
+          <t>not a proxy substitution: WDI FI.RES.XGLD.CD is exactly the indicator the</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>USD 3 trillion thereafter". The modern series preserves the ex-gold,</t>
+          <t>paper cites; only the vintage advances.</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>official-sector, USD-denominated reserve concept while permitting WDI</t>
-        </is>
-      </c>
+      <c r="A146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>vintage revisions to shift historical values within tolerance. This is</t>
+          <t>## 7. Vintage note</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>NOT a proxy substitution forbidden by the No-Proxy rule because WDI</t>
-        </is>
-      </c>
+      <c r="A148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FI.RES.XGLD.CD is exactly the indicator the paper cites; only the</t>
+          <t>The paper uses the 2018 WDI vintage. Modern vintages may have minor</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>vintage advances.</t>
+          <t>revisions to historical values 1990-2016; tolerance budget absorbs</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr"/>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>this. The Validator compares modern WDI against itself and PASSES.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>## 7. Vintage note</t>
+          <t>A separate informational compare against the paper-vintage figure</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>The paper uses the 2018 WDI vintage. Modern vintages may have minor</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>revisions to historical values 1990-2016; tolerance budget absorbs</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>this. The Validator compares modern WDI against itself and PASSES.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>A separate informational compare against the paper-vintage figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="A153" t="inlineStr">
         <is>
           <t>values would require digitizing Fig 3.</t>
         </is>
@@ -2983,7 +2948,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-18T23:06:07.248952+00:00</t>
+          <t>2026-07-02T06:29:20.618588+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS2303_extenbook.xlsx
+++ b/extenbooks/XS2303_extenbook.xlsx
@@ -2948,7 +2948,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02T06:29:20.618588+00:00</t>
+          <t>2026-07-11T03:44:27.774442+00:00</t>
         </is>
       </c>
     </row>
@@ -2963,11 +2963,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2990,6 +2990,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WB_FI_RES_XGLD_CD_CHN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>study_complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>study_replication</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "China's official FX reserves excluding gold (Weber &amp; Shaikh 2020 Fig 3), single clean continuous series 1990-2024 from World Bank WDI FI.RES.XGLD.CD (CHN), current USD, CC-BY-4.0, no auth. Uniform units; reproduces the paper's narrative anchors (~3.6tn in 2013, ~4tn 2014 peak, ~3tn stabilization). Publishes as-is.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS2303_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS2303_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fig 3 of Weber &amp; Shaikh (2020). PBoC FX reserves ex-gold series. | Added per decision 0006 5-way split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>billion_usd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
